--- a/apps/cmdb/model_migrate/model_config.xlsx
+++ b/apps/cmdb/model_migrate/model_config.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowHeight="15520" tabRatio="896" firstSheet="3" activeTab="11"/>
+    <workbookView windowHeight="15520" tabRatio="896" firstSheet="33" activeTab="39"/>
   </bookViews>
   <sheets>
     <sheet name="classifications" sheetId="97" r:id="rId1"/>
@@ -12008,7 +12008,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -12056,7 +12056,7 @@
         <v>1</v>
       </c>
       <c r="H8" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -12675,7 +12675,7 @@
         <v>211</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="E10" t="s">
         <v>169</v>
